--- a/artfynd/A 54802-2024 artfynd.xlsx
+++ b/artfynd/A 54802-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150290</v>
+        <v>121150289</v>
       </c>
       <c r="B2" t="n">
-        <v>91957</v>
+        <v>91259</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670994</v>
+        <v>671077</v>
       </c>
       <c r="R2" t="n">
-        <v>7184352</v>
+        <v>7184250</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150289</v>
+        <v>121150291</v>
       </c>
       <c r="B3" t="n">
-        <v>91249</v>
+        <v>91973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671077</v>
+        <v>671091</v>
       </c>
       <c r="R3" t="n">
-        <v>7184250</v>
+        <v>7184255</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150291</v>
+        <v>121150290</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>91967</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671091</v>
+        <v>670994</v>
       </c>
       <c r="R4" t="n">
-        <v>7184255</v>
+        <v>7184352</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 54802-2024 artfynd.xlsx
+++ b/artfynd/A 54802-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150289</v>
+        <v>121150290</v>
       </c>
       <c r="B2" t="n">
-        <v>91259</v>
+        <v>91967</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>671077</v>
+        <v>670994</v>
       </c>
       <c r="R2" t="n">
-        <v>7184250</v>
+        <v>7184352</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150291</v>
+        <v>121150289</v>
       </c>
       <c r="B3" t="n">
-        <v>91973</v>
+        <v>91259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671091</v>
+        <v>671077</v>
       </c>
       <c r="R3" t="n">
-        <v>7184255</v>
+        <v>7184250</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150290</v>
+        <v>121150291</v>
       </c>
       <c r="B4" t="n">
-        <v>91967</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670994</v>
+        <v>671091</v>
       </c>
       <c r="R4" t="n">
-        <v>7184352</v>
+        <v>7184255</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 54802-2024 artfynd.xlsx
+++ b/artfynd/A 54802-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150290</v>
+        <v>121150289</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>91271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670994</v>
+        <v>671077</v>
       </c>
       <c r="R2" t="n">
-        <v>7184352</v>
+        <v>7184250</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150289</v>
+        <v>121150290</v>
       </c>
       <c r="B3" t="n">
-        <v>91259</v>
+        <v>91979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671077</v>
+        <v>670994</v>
       </c>
       <c r="R3" t="n">
-        <v>7184250</v>
+        <v>7184352</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121150291</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54802-2024 artfynd.xlsx
+++ b/artfynd/A 54802-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150289</v>
+        <v>121150290</v>
       </c>
       <c r="B2" t="n">
-        <v>91271</v>
+        <v>91980</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>671077</v>
+        <v>670994</v>
       </c>
       <c r="R2" t="n">
-        <v>7184250</v>
+        <v>7184352</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150290</v>
+        <v>121150289</v>
       </c>
       <c r="B3" t="n">
-        <v>91979</v>
+        <v>91272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670994</v>
+        <v>671077</v>
       </c>
       <c r="R3" t="n">
-        <v>7184352</v>
+        <v>7184250</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121150291</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54802-2024 artfynd.xlsx
+++ b/artfynd/A 54802-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150290</v>
+        <v>121150289</v>
       </c>
       <c r="B2" t="n">
-        <v>91980</v>
+        <v>91275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670994</v>
+        <v>671077</v>
       </c>
       <c r="R2" t="n">
-        <v>7184352</v>
+        <v>7184250</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150289</v>
+        <v>121150291</v>
       </c>
       <c r="B3" t="n">
-        <v>91272</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671077</v>
+        <v>671091</v>
       </c>
       <c r="R3" t="n">
-        <v>7184250</v>
+        <v>7184255</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150291</v>
+        <v>121150290</v>
       </c>
       <c r="B4" t="n">
-        <v>91986</v>
+        <v>91983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671091</v>
+        <v>670994</v>
       </c>
       <c r="R4" t="n">
-        <v>7184255</v>
+        <v>7184352</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 54802-2024 artfynd.xlsx
+++ b/artfynd/A 54802-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150289</v>
+        <v>121150291</v>
       </c>
       <c r="B2" t="n">
-        <v>91275</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>671077</v>
+        <v>671091</v>
       </c>
       <c r="R2" t="n">
-        <v>7184250</v>
+        <v>7184255</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150291</v>
+        <v>121150290</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>91983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671091</v>
+        <v>670994</v>
       </c>
       <c r="R3" t="n">
-        <v>7184255</v>
+        <v>7184352</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150290</v>
+        <v>121150289</v>
       </c>
       <c r="B4" t="n">
-        <v>91983</v>
+        <v>91275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670994</v>
+        <v>671077</v>
       </c>
       <c r="R4" t="n">
-        <v>7184352</v>
+        <v>7184250</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 54802-2024 artfynd.xlsx
+++ b/artfynd/A 54802-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150291</v>
+        <v>121150289</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>671091</v>
+        <v>671077</v>
       </c>
       <c r="R2" t="n">
-        <v>7184255</v>
+        <v>7184250</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,12 +784,7 @@
         <v>121150290</v>
       </c>
       <c r="B3" t="n">
-        <v>91983</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150289</v>
+        <v>121150291</v>
       </c>
       <c r="B4" t="n">
-        <v>91275</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671077</v>
+        <v>671091</v>
       </c>
       <c r="R4" t="n">
-        <v>7184250</v>
+        <v>7184255</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 54802-2024 artfynd.xlsx
+++ b/artfynd/A 54802-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150289</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150290</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150291</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>